--- a/data/contractors/derived-4700134228/sources/expense_rates.xlsx
+++ b/data/contractors/derived-4700134228/sources/expense_rates.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ставки" sheetId="1" r:id="Rcd6a6a2130b54051"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ставки" sheetId="1" r:id="Rd760af70aad24ca7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -424,14 +424,14 @@
         <x:v>Резерв на отпуска</x:v>
       </x:c>
       <x:c r="C5" s="5" t="n">
-        <x:v>9.226190476190476</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D5" s="3" t="str">
         <x:v>rate</x:v>
       </x:c>
       <x:c r="E5" s="3" t="str"/>
       <x:c r="F5" s="3" t="str">
-        <x:v>Расчётный сценарий 4700134228: Исходная модель, Детальная модель!F50 · Согласованные 8% годового ФОТ/мес.; F50 = 9,22619% на другой базе</x:v>
+        <x:v>Решение пользователя: 8% годового ФОТ начисляются ежемесячно; ставка процента не удваивается.</x:v>
       </x:c>
       <x:c r="G5" s="3" t="str"/>
       <x:c r="H5" s="3" t="n">
@@ -808,14 +808,14 @@
         <x:v>Резерв на отпуска</x:v>
       </x:c>
       <x:c r="C17" s="5" t="n">
-        <x:v>9.226190476190476</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D17" s="3" t="str">
         <x:v>rate</x:v>
       </x:c>
       <x:c r="E17" s="3" t="str"/>
       <x:c r="F17" s="3" t="str">
-        <x:v>Расчётный сценарий 4700134228: Исходная модель, Детальная модель!F63 · Согласованные 8% годового ФОТ/мес.; F63 = 9,22619% на другой базе</x:v>
+        <x:v>Решение пользователя: 8% годового ФОТ начисляются ежемесячно; ставка процента не удваивается.</x:v>
       </x:c>
       <x:c r="G17" s="3" t="str"/>
       <x:c r="H17" s="3" t="n">
